--- a/archives_posts/votation_allegement_primes2024_vox/LCA_analyse_vox2024.xlsx
+++ b/archives_posts/votation_allegement_primes2024_vox/LCA_analyse_vox2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\celalguney\archives_posts\votation_allegement_primes2024_vox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D129962A-AA16-42EF-85C6-AEC83741B41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E475C314-E7AF-4FE2-8A29-8708C6DA2DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LCA 7 classes" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6974" uniqueCount="2167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6995" uniqueCount="2188">
   <si>
     <t>[JJJJ]</t>
   </si>
@@ -6614,6 +6614,69 @@
   </si>
   <si>
     <t>Classe moyenne conservatrice</t>
+  </si>
+  <si>
+    <t>Bloc social</t>
+  </si>
+  <si>
+    <t>Groupe socio-politique</t>
+  </si>
+  <si>
+    <t>Groupe socio-économique</t>
+  </si>
+  <si>
+    <t>Demandes politiques</t>
+  </si>
+  <si>
+    <t>Conservateurs (37,6%)</t>
+  </si>
+  <si>
+    <t>Néolibéraux (18,6%)</t>
+  </si>
+  <si>
+    <t>Contre toute augmentation fiscale; pour lier les primes d'assurance-maladie au revenu et créer une caisse unique; contre les réformes néolibérales.</t>
+  </si>
+  <si>
+    <t>Contre toute augmentation fiscale; contre lier les primes d'assurance-maladie au revenu et créer une caisse unique; fortement pour les réformes néolibérales</t>
+  </si>
+  <si>
+    <t>En faveur d'une augmentation fiscale; pour lier les primes d'assurance-maldie au revenu et la création d'une caisse unique; contre les réformes néolibérales.</t>
+  </si>
+  <si>
+    <t>Contre toute augmentation fiscale; pour lier les primes d'assurance-maldie au revenu et la création d'une caisse unique; contre les réformes néolibérales.</t>
+  </si>
+  <si>
+    <t>Employés à haut niveau de revenu et d'éducation exerçant une fonction de supervision (cadre, manager). Forte présence en Suisse-alémanique</t>
+  </si>
+  <si>
+    <t>Employés sans fonction de supervision à haut niveau d'éducation et niveau de revenu moyen. Légère surreprésentation en Suisse-alémanique</t>
+  </si>
+  <si>
+    <t>Employé à niveau d'éducation et de revenu moyen à faible. Pas de surreprésentation régionale ou linguistique</t>
+  </si>
+  <si>
+    <t>Employés à niveau d'éducation moyen et niveau de revenu plutôt faible. Forte représentation de Romands et Tessinois</t>
+  </si>
+  <si>
+    <t>Libéral-conservateur</t>
+  </si>
+  <si>
+    <t>Bloc de gauche</t>
+  </si>
+  <si>
+    <t>Réformiste socialiste (18,5%)</t>
+  </si>
+  <si>
+    <t>Réformiste socialiste anti-fiscalité (7,5%)</t>
+  </si>
+  <si>
+    <t>En marge des deux blocs</t>
+  </si>
+  <si>
+    <t>Sans opinion (pour le cluster 7); indécis sur la plupart des variables (cluster 4) ou bien réponse uniquement des réponses favorables (cluster 7)</t>
+  </si>
+  <si>
+    <t>Clusters 4 (8,3%); cluster 6 (6,8%) et cluster 7 (2,7%)</t>
   </si>
 </sst>
 </file>
@@ -6875,7 +6938,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="96">
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -7155,6 +7218,12 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -8415,7 +8484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B3EA10-774F-4FBE-BD7A-ED829CD96A29}">
-  <dimension ref="A1:K849"/>
+  <dimension ref="A1:O849"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="36.81640625" style="25" customWidth="1"/>
@@ -8423,10 +8492,15 @@
     <col min="3" max="3" width="14.81640625" style="25" customWidth="1"/>
     <col min="4" max="6" width="10.6328125" style="25"/>
     <col min="7" max="7" width="11.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.6328125" style="25"/>
+    <col min="8" max="11" width="10.6328125" style="25"/>
+    <col min="12" max="12" width="17.08984375" style="25" customWidth="1"/>
+    <col min="13" max="13" width="30" style="25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" style="25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.7265625" style="25" customWidth="1"/>
+    <col min="16" max="16384" width="10.6328125" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="43.5">
+    <row r="1" spans="1:15" ht="43.5">
       <c r="B1" s="84" t="s">
         <v>2166</v>
       </c>
@@ -8449,7 +8523,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:15">
       <c r="A2" s="26"/>
       <c r="B2" s="70" t="s">
         <v>1971</v>
@@ -8476,7 +8550,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:15">
       <c r="A3" s="72" t="s">
         <v>1979</v>
       </c>
@@ -8503,7 +8577,7 @@
       </c>
       <c r="I3" s="73"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:15">
       <c r="A4" s="72" t="s">
         <v>1980</v>
       </c>
@@ -8516,7 +8590,7 @@
       <c r="H4" s="73"/>
       <c r="I4" s="73"/>
     </row>
-    <row r="5" spans="1:9" ht="29">
+    <row r="5" spans="1:15" ht="29">
       <c r="A5" s="72" t="s">
         <v>1784</v>
       </c>
@@ -8528,8 +8602,20 @@
       <c r="G5" s="73"/>
       <c r="H5" s="73"/>
       <c r="I5" s="73"/>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="L5" s="25" t="s">
+        <v>2167</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>2168</v>
+      </c>
+      <c r="N5" s="25" t="s">
+        <v>2169</v>
+      </c>
+      <c r="O5" s="25" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="72.5">
       <c r="A6" s="70" t="s">
         <v>2138</v>
       </c>
@@ -8557,8 +8643,20 @@
       <c r="I6" s="73">
         <v>0.28050000000000003</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="L6" s="95" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>2171</v>
+      </c>
+      <c r="N6" s="83" t="s">
+        <v>2179</v>
+      </c>
+      <c r="O6" s="83" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="87">
       <c r="A7" s="70" t="s">
         <v>1981</v>
       </c>
@@ -8586,8 +8684,18 @@
       <c r="I7" s="73">
         <v>0.14580000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="L7" s="95"/>
+      <c r="M7" s="25" t="s">
+        <v>2172</v>
+      </c>
+      <c r="N7" s="83" t="s">
+        <v>2177</v>
+      </c>
+      <c r="O7" s="83" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="87">
       <c r="A8" s="70" t="s">
         <v>2139</v>
       </c>
@@ -8615,8 +8723,20 @@
       <c r="I8" s="73">
         <v>0.57369999999999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="L8" s="94" t="s">
+        <v>2182</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>2183</v>
+      </c>
+      <c r="N8" s="83" t="s">
+        <v>2178</v>
+      </c>
+      <c r="O8" s="83" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="87">
       <c r="A9" s="72" t="s">
         <v>1788</v>
       </c>
@@ -8628,8 +8748,18 @@
       <c r="G9" s="73"/>
       <c r="H9" s="73"/>
       <c r="I9" s="73"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="L9" s="94"/>
+      <c r="M9" s="25" t="s">
+        <v>2184</v>
+      </c>
+      <c r="N9" s="83" t="s">
+        <v>2180</v>
+      </c>
+      <c r="O9" s="83" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="72.5">
       <c r="A10" s="70" t="s">
         <v>2138</v>
       </c>
@@ -8657,8 +8787,17 @@
       <c r="I10" s="73">
         <v>0.1968</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="L10" s="83" t="s">
+        <v>2185</v>
+      </c>
+      <c r="M10" s="83" t="s">
+        <v>2187</v>
+      </c>
+      <c r="O10" s="83" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="70" t="s">
         <v>1981</v>
       </c>
@@ -8687,7 +8826,7 @@
         <v>0.14199999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:15">
       <c r="A12" s="70" t="s">
         <v>2139</v>
       </c>
@@ -8716,7 +8855,7 @@
         <v>0.6613</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="29">
+    <row r="13" spans="1:15" ht="29">
       <c r="A13" s="72" t="s">
         <v>1792</v>
       </c>
@@ -8729,7 +8868,7 @@
       <c r="H13" s="73"/>
       <c r="I13" s="73"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:15">
       <c r="A14" s="70" t="s">
         <v>2138</v>
       </c>
@@ -8758,7 +8897,7 @@
         <v>0.51859999999999995</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:15">
       <c r="A15" s="70" t="s">
         <v>1981</v>
       </c>
@@ -8787,7 +8926,7 @@
         <v>0.11559999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:15">
       <c r="A16" s="70" t="s">
         <v>2139</v>
       </c>
@@ -12669,12 +12808,12 @@
         <v>1.46E-2</v>
       </c>
       <c r="J161" s="79">
-        <f>SUM(B161:B168)</f>
-        <v>0.49019999999999997</v>
+        <f>SUM(F161:F165)</f>
+        <v>0.31030000000000002</v>
       </c>
       <c r="K161" s="79">
-        <f>SUM(I161:I168)</f>
-        <v>0.47660000000000002</v>
+        <f>SUM(I161:I165)</f>
+        <v>0.25980000000000003</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -24692,8 +24831,8 @@
         <v>2.1299999999999999E-2</v>
       </c>
       <c r="J598" s="79">
-        <f>SUM(B598:B602)</f>
-        <v>0.23960000000000001</v>
+        <f>SUM(E598:E602)</f>
+        <v>0.2581</v>
       </c>
       <c r="K598" s="79">
         <f>SUM(I598:I602)</f>
@@ -24729,8 +24868,8 @@
         <v>2.3900000000000001E-2</v>
       </c>
       <c r="J599" s="79">
-        <f>SUM(B604:B608)</f>
-        <v>0.36049999999999999</v>
+        <f>SUM(E604:E608)</f>
+        <v>0.30409999999999998</v>
       </c>
       <c r="K599" s="79">
         <f>SUM(I604:I608)</f>
@@ -31494,6 +31633,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="L8:L9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/archives_posts/votation_allegement_primes2024_vox/LCA_analyse_vox2024.xlsx
+++ b/archives_posts/votation_allegement_primes2024_vox/LCA_analyse_vox2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\celalguney\archives_posts\votation_allegement_primes2024_vox\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celal\Documents\GitHub\celalguney\archives_posts\votation_allegement_primes2024_vox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E475C314-E7AF-4FE2-8A29-8708C6DA2DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D53B6B-4BEA-467D-BBF6-4A2A2DB664E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="570" yWindow="270" windowWidth="28485" windowHeight="14970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LCA 7 classes" sheetId="5" r:id="rId1"/>
@@ -22,24 +22,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Codebook!$A$1:$E$2231</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6995" uniqueCount="2188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6996" uniqueCount="2189">
   <si>
     <t>[JJJJ]</t>
   </si>
@@ -6628,12 +6615,6 @@
     <t>Demandes politiques</t>
   </si>
   <si>
-    <t>Conservateurs (37,6%)</t>
-  </si>
-  <si>
-    <t>Néolibéraux (18,6%)</t>
-  </si>
-  <si>
     <t>Contre toute augmentation fiscale; pour lier les primes d'assurance-maladie au revenu et créer une caisse unique; contre les réformes néolibérales.</t>
   </si>
   <si>
@@ -6664,12 +6645,6 @@
     <t>Bloc de gauche</t>
   </si>
   <si>
-    <t>Réformiste socialiste (18,5%)</t>
-  </si>
-  <si>
-    <t>Réformiste socialiste anti-fiscalité (7,5%)</t>
-  </si>
-  <si>
     <t>En marge des deux blocs</t>
   </si>
   <si>
@@ -6677,6 +6652,21 @@
   </si>
   <si>
     <t>Clusters 4 (8,3%); cluster 6 (6,8%) et cluster 7 (2,7%)</t>
+  </si>
+  <si>
+    <t>Réformiste socialiste (cluster 3: 18,5%)</t>
+  </si>
+  <si>
+    <t>Réformiste socialiste anti-fiscalité (cluster 5: 7,5%)</t>
+  </si>
+  <si>
+    <t>Néolibéraux (cluster 2: 18,6%)</t>
+  </si>
+  <si>
+    <t>Conservateurs (cluster 1: 37,6%)</t>
+  </si>
+  <si>
+    <t>Niveau d'éducation et de revenu faible ou moyen</t>
   </si>
 </sst>
 </file>
@@ -7213,17 +7203,17 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -8485,22 +8475,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B3EA10-774F-4FBE-BD7A-ED829CD96A29}">
   <dimension ref="A1:O849"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.59765625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="36.81640625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="25" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" style="25" customWidth="1"/>
-    <col min="4" max="6" width="10.6328125" style="25"/>
-    <col min="7" max="7" width="11.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="10.6328125" style="25"/>
-    <col min="12" max="12" width="17.08984375" style="25" customWidth="1"/>
-    <col min="13" max="13" width="30" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.796875" style="25" customWidth="1"/>
+    <col min="2" max="2" width="14.46484375" style="25" customWidth="1"/>
+    <col min="3" max="3" width="14.796875" style="25" customWidth="1"/>
+    <col min="4" max="6" width="10.59765625" style="25"/>
+    <col min="7" max="7" width="11.46484375" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="10.59765625" style="25"/>
+    <col min="12" max="12" width="17.06640625" style="25" customWidth="1"/>
+    <col min="13" max="13" width="27.3984375" style="25" customWidth="1"/>
     <col min="14" max="14" width="23" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.7265625" style="25" customWidth="1"/>
-    <col min="16" max="16384" width="10.6328125" style="25"/>
+    <col min="15" max="15" width="30.73046875" style="25" customWidth="1"/>
+    <col min="16" max="16384" width="10.59765625" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="43.5">
+    <row r="1" spans="1:15" ht="42.75">
       <c r="B1" s="84" t="s">
         <v>2166</v>
       </c>
@@ -8590,7 +8580,7 @@
       <c r="H4" s="73"/>
       <c r="I4" s="73"/>
     </row>
-    <row r="5" spans="1:15" ht="29">
+    <row r="5" spans="1:15" ht="28.5">
       <c r="A5" s="72" t="s">
         <v>1784</v>
       </c>
@@ -8615,7 +8605,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="72.5">
+    <row r="6" spans="1:15" ht="71.25">
       <c r="A6" s="70" t="s">
         <v>2138</v>
       </c>
@@ -8643,20 +8633,20 @@
       <c r="I6" s="73">
         <v>0.28050000000000003</v>
       </c>
-      <c r="L6" s="95" t="s">
-        <v>2181</v>
+      <c r="L6" s="92" t="s">
+        <v>2179</v>
       </c>
       <c r="M6" s="25" t="s">
+        <v>2187</v>
+      </c>
+      <c r="N6" s="83" t="s">
+        <v>2177</v>
+      </c>
+      <c r="O6" s="83" t="s">
         <v>2171</v>
       </c>
-      <c r="N6" s="83" t="s">
-        <v>2179</v>
-      </c>
-      <c r="O6" s="83" t="s">
-        <v>2173</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="87">
+    </row>
+    <row r="7" spans="1:15" ht="85.5">
       <c r="A7" s="70" t="s">
         <v>1981</v>
       </c>
@@ -8684,18 +8674,18 @@
       <c r="I7" s="73">
         <v>0.14580000000000001</v>
       </c>
-      <c r="L7" s="95"/>
+      <c r="L7" s="92"/>
       <c r="M7" s="25" t="s">
+        <v>2186</v>
+      </c>
+      <c r="N7" s="83" t="s">
+        <v>2175</v>
+      </c>
+      <c r="O7" s="83" t="s">
         <v>2172</v>
       </c>
-      <c r="N7" s="83" t="s">
-        <v>2177</v>
-      </c>
-      <c r="O7" s="83" t="s">
-        <v>2174</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="87">
+    </row>
+    <row r="8" spans="1:15" ht="85.5">
       <c r="A8" s="70" t="s">
         <v>2139</v>
       </c>
@@ -8723,20 +8713,20 @@
       <c r="I8" s="73">
         <v>0.57369999999999999</v>
       </c>
-      <c r="L8" s="94" t="s">
-        <v>2182</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>2183</v>
+      <c r="L8" s="93" t="s">
+        <v>2180</v>
+      </c>
+      <c r="M8" s="83" t="s">
+        <v>2184</v>
       </c>
       <c r="N8" s="83" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
       <c r="O8" s="83" t="s">
-        <v>2175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="87">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="71.25">
       <c r="A9" s="72" t="s">
         <v>1788</v>
       </c>
@@ -8748,18 +8738,18 @@
       <c r="G9" s="73"/>
       <c r="H9" s="73"/>
       <c r="I9" s="73"/>
-      <c r="L9" s="94"/>
-      <c r="M9" s="25" t="s">
-        <v>2184</v>
+      <c r="L9" s="93"/>
+      <c r="M9" s="83" t="s">
+        <v>2185</v>
       </c>
       <c r="N9" s="83" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="O9" s="83" t="s">
-        <v>2176</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="72.5">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="71.25">
       <c r="A10" s="70" t="s">
         <v>2138</v>
       </c>
@@ -8788,13 +8778,16 @@
         <v>0.1968</v>
       </c>
       <c r="L10" s="83" t="s">
-        <v>2185</v>
+        <v>2181</v>
       </c>
       <c r="M10" s="83" t="s">
-        <v>2187</v>
+        <v>2183</v>
+      </c>
+      <c r="N10" s="83" t="s">
+        <v>2188</v>
       </c>
       <c r="O10" s="83" t="s">
-        <v>2186</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -8855,7 +8848,7 @@
         <v>0.6613</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="29">
+    <row r="13" spans="1:15" ht="28.5">
       <c r="A13" s="72" t="s">
         <v>1792</v>
       </c>
@@ -9155,7 +9148,7 @@
         <v>0.80449999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="29">
+    <row r="25" spans="1:9" ht="28.5">
       <c r="A25" s="72" t="s">
         <v>1804</v>
       </c>
@@ -9255,7 +9248,7 @@
         <v>0.59540000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="29">
+    <row r="29" spans="1:9" ht="28.5">
       <c r="A29" s="72" t="s">
         <v>1808</v>
       </c>
@@ -9355,7 +9348,7 @@
         <v>0.65390000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="29">
+    <row r="33" spans="1:9" ht="28.5">
       <c r="A33" s="72" t="s">
         <v>1812</v>
       </c>
@@ -10416,7 +10409,7 @@
         <v>4.1700000000000001E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="29">
+    <row r="74" spans="1:9" ht="28.5">
       <c r="A74" s="70" t="s">
         <v>2006</v>
       </c>
@@ -10948,7 +10941,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="29">
+    <row r="94" spans="1:9" ht="28.5">
       <c r="A94" s="70" t="s">
         <v>203</v>
       </c>
@@ -11193,7 +11186,7 @@
       <c r="H102" s="73"/>
       <c r="I102" s="73"/>
     </row>
-    <row r="103" spans="1:9" ht="29">
+    <row r="103" spans="1:9" ht="28.5">
       <c r="A103" s="70" t="s">
         <v>209</v>
       </c>
@@ -11396,7 +11389,7 @@
         <v>2.7099999999999999E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="29">
+    <row r="110" spans="1:9" ht="28.5">
       <c r="A110" s="70" t="s">
         <v>2025</v>
       </c>
@@ -11583,7 +11576,7 @@
         <v>7.8299999999999995E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="29">
+    <row r="117" spans="1:9" ht="28.5">
       <c r="A117" s="70" t="s">
         <v>826</v>
       </c>
@@ -11728,7 +11721,7 @@
         <v>2.5499999999999998E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="29">
+    <row r="122" spans="1:9" ht="28.5">
       <c r="A122" s="70" t="s">
         <v>46</v>
       </c>
@@ -11757,7 +11750,7 @@
         <v>0.2324</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="29">
+    <row r="123" spans="1:9" ht="28.5">
       <c r="A123" s="70" t="s">
         <v>645</v>
       </c>
@@ -11915,7 +11908,7 @@
         <v>4.9700000000000001E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="29">
+    <row r="129" spans="1:9" ht="28.5">
       <c r="A129" s="70" t="s">
         <v>2030</v>
       </c>
@@ -12260,7 +12253,7 @@
         <v>0.50970000000000004</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="29">
+    <row r="142" spans="1:9" ht="28.5">
       <c r="A142" s="70" t="s">
         <v>2033</v>
       </c>
@@ -12389,7 +12382,7 @@
       <c r="H146" s="73"/>
       <c r="I146" s="73"/>
     </row>
-    <row r="147" spans="1:9" ht="29">
+    <row r="147" spans="1:9" ht="28.5">
       <c r="A147" s="70" t="s">
         <v>209</v>
       </c>
@@ -12592,7 +12585,7 @@
         <v>1.0800000000000001E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="29">
+    <row r="154" spans="1:9" ht="28.5">
       <c r="A154" s="70" t="s">
         <v>2025</v>
       </c>
@@ -13251,7 +13244,7 @@
         <v>0.1573</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="87">
+    <row r="177" spans="1:9" ht="71.25">
       <c r="A177" s="72" t="s">
         <v>2155</v>
       </c>
@@ -14174,7 +14167,7 @@
         <v>0.1391</v>
       </c>
     </row>
-    <row r="210" spans="1:9" s="78" customFormat="1" ht="29">
+    <row r="210" spans="1:9" s="78" customFormat="1" ht="28.5">
       <c r="A210" s="77" t="s">
         <v>2159</v>
       </c>
@@ -14245,7 +14238,7 @@
         <v>0.3327</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="29">
+    <row r="213" spans="1:9" ht="28.5">
       <c r="A213" s="70" t="s">
         <v>164</v>
       </c>
@@ -15283,7 +15276,7 @@
         <v>0.34799999999999998</v>
       </c>
     </row>
-    <row r="251" spans="1:9" s="78" customFormat="1" ht="29">
+    <row r="251" spans="1:9" s="78" customFormat="1" ht="28.5">
       <c r="A251" s="77" t="s">
         <v>2156</v>
       </c>
@@ -15354,7 +15347,7 @@
         <v>0.36230000000000001</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="29">
+    <row r="254" spans="1:9" ht="28.5">
       <c r="A254" s="70" t="s">
         <v>164</v>
       </c>
@@ -16002,7 +15995,7 @@
         <v>0.98219999999999996</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="29">
+    <row r="278" spans="1:9" ht="28.5">
       <c r="A278" s="72" t="s">
         <v>2157</v>
       </c>
@@ -16073,7 +16066,7 @@
         <v>0.44409999999999999</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="29">
+    <row r="281" spans="1:9" ht="28.5">
       <c r="A281" s="70" t="s">
         <v>164</v>
       </c>
@@ -17082,7 +17075,7 @@
         <v>0.34799999999999998</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="29">
+    <row r="318" spans="1:9" ht="28.5">
       <c r="A318" s="72" t="s">
         <v>2158</v>
       </c>
@@ -17153,7 +17146,7 @@
         <v>0.1273</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="29">
+    <row r="321" spans="1:9" ht="28.5">
       <c r="A321" s="70" t="s">
         <v>164</v>
       </c>
@@ -31400,7 +31393,7 @@
         <v>5.3499999999999999E-2</v>
       </c>
     </row>
-    <row r="842" spans="1:9" ht="29">
+    <row r="842" spans="1:9" ht="28.5">
       <c r="A842" s="70" t="s">
         <v>2006</v>
       </c>
@@ -31644,16 +31637,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2231"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.36328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.7265625" style="33" customWidth="1"/>
-    <col min="4" max="4" width="94.08984375" style="33" customWidth="1"/>
-    <col min="5" max="5" width="94.08984375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="25.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.73046875" style="33" customWidth="1"/>
+    <col min="4" max="4" width="94.06640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="94.06640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="65" customFormat="1" ht="18.5">
+    <row r="1" spans="1:5" s="65" customFormat="1" ht="18">
       <c r="A1" s="4" t="s">
         <v>661</v>
       </c>
@@ -31728,7 +31721,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="43.5">
+    <row r="6" spans="1:5" ht="42.75">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>235</v>
@@ -31788,7 +31781,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="29">
+    <row r="10" spans="1:5" ht="28.5">
       <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
         <v>238</v>
@@ -31878,7 +31871,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="29">
+    <row r="16" spans="1:5" ht="28.5">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
         <v>654</v>
@@ -35793,7 +35786,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="285" spans="2:5" s="25" customFormat="1" ht="43.5">
+    <row r="285" spans="2:5" s="25" customFormat="1" ht="42.75">
       <c r="B285" s="5">
         <v>55</v>
       </c>
@@ -36745,7 +36738,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="351" spans="1:5" s="25" customFormat="1" ht="43.5">
+    <row r="351" spans="1:5" s="25" customFormat="1" ht="42.75">
       <c r="B351" s="5">
         <v>55</v>
       </c>
@@ -37200,7 +37193,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="58">
+    <row r="383" spans="1:5" ht="57">
       <c r="A383" s="25"/>
       <c r="B383" s="25" t="s">
         <v>683</v>
@@ -37305,7 +37298,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="58">
+    <row r="390" spans="1:5" ht="57">
       <c r="A390" s="25"/>
       <c r="B390" s="25" t="s">
         <v>684</v>
@@ -37410,7 +37403,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="58">
+    <row r="397" spans="1:5" ht="57">
       <c r="A397" s="5"/>
       <c r="B397" s="25" t="s">
         <v>685</v>
@@ -37515,7 +37508,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="29">
+    <row r="404" spans="1:5" ht="28.5">
       <c r="A404" s="5"/>
       <c r="B404" s="25" t="s">
         <v>148</v>
@@ -38010,7 +38003,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="29">
+    <row r="437" spans="1:5">
       <c r="A437" s="5"/>
       <c r="B437" s="5">
         <v>35</v>
@@ -38085,7 +38078,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="29">
+    <row r="442" spans="1:5" ht="28.5">
       <c r="A442" s="5"/>
       <c r="B442" s="5">
         <v>42</v>
@@ -38713,7 +38706,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="29">
+    <row r="484" spans="1:5">
       <c r="A484" s="5"/>
       <c r="B484" s="5">
         <v>35</v>
@@ -38788,7 +38781,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="29">
+    <row r="489" spans="1:5" ht="28.5">
       <c r="A489" s="5"/>
       <c r="B489" s="5">
         <v>42</v>
@@ -39566,7 +39559,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="543" spans="2:5" ht="29">
+    <row r="543" spans="2:5" ht="28.5">
       <c r="B543">
         <v>45</v>
       </c>
@@ -39608,7 +39601,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="29">
+    <row r="546" spans="1:5" ht="28.5">
       <c r="B546">
         <v>51</v>
       </c>
@@ -40282,7 +40275,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="594" spans="2:5" ht="29">
+    <row r="594" spans="2:5" ht="28.5">
       <c r="B594">
         <v>45</v>
       </c>
@@ -40324,7 +40317,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="597" spans="2:5" ht="29">
+    <row r="597" spans="2:5" ht="28.5">
       <c r="B597">
         <v>51</v>
       </c>
@@ -40653,7 +40646,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="58">
+    <row r="620" spans="1:5" ht="57">
       <c r="A620" s="5"/>
       <c r="B620" s="25" t="s">
         <v>776</v>
@@ -40758,7 +40751,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="58">
+    <row r="627" spans="1:5" ht="57">
       <c r="A627" s="5"/>
       <c r="B627" s="25" t="s">
         <v>777</v>
@@ -40863,7 +40856,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="58">
+    <row r="634" spans="1:5" ht="57">
       <c r="A634" s="5"/>
       <c r="B634" s="25" t="s">
         <v>778</v>
@@ -40968,7 +40961,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="29">
+    <row r="641" spans="1:5" ht="28.5">
       <c r="A641" s="5"/>
       <c r="B641" s="25" t="s">
         <v>779</v>
@@ -41417,7 +41410,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="672" spans="2:5" ht="29">
+    <row r="672" spans="2:5">
       <c r="B672">
         <v>34</v>
       </c>
@@ -41473,7 +41466,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="676" spans="2:5" ht="29">
+    <row r="676" spans="2:5" ht="28.5">
       <c r="B676">
         <v>52</v>
       </c>
@@ -41557,7 +41550,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="682" spans="2:5" ht="29">
+    <row r="682" spans="2:5" ht="28.5">
       <c r="B682">
         <v>62</v>
       </c>
@@ -41571,7 +41564,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="683" spans="2:5" ht="29">
+    <row r="683" spans="2:5" ht="28.5">
       <c r="B683">
         <v>63</v>
       </c>
@@ -42021,7 +42014,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="715" spans="2:5" ht="29">
+    <row r="715" spans="2:5">
       <c r="B715">
         <v>34</v>
       </c>
@@ -42077,7 +42070,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="719" spans="2:5" ht="29">
+    <row r="719" spans="2:5" ht="28.5">
       <c r="B719">
         <v>52</v>
       </c>
@@ -42161,7 +42154,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="725" spans="2:5" ht="29">
+    <row r="725" spans="2:5" ht="28.5">
       <c r="B725">
         <v>62</v>
       </c>
@@ -42175,7 +42168,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="726" spans="2:5" ht="29">
+    <row r="726" spans="2:5" ht="28.5">
       <c r="B726">
         <v>63</v>
       </c>
@@ -42667,7 +42660,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="761" spans="2:5" ht="29">
+    <row r="761" spans="2:5" ht="28.5">
       <c r="B761">
         <v>35</v>
       </c>
@@ -42737,7 +42730,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="766" spans="2:5" ht="29">
+    <row r="766" spans="2:5" ht="28.5">
       <c r="B766">
         <v>43</v>
       </c>
@@ -43243,7 +43236,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="802" spans="2:5" ht="29">
+    <row r="802" spans="2:5" ht="28.5">
       <c r="B802">
         <v>35</v>
       </c>
@@ -43313,7 +43306,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="807" spans="2:5" ht="29">
+    <row r="807" spans="2:5" ht="28.5">
       <c r="B807">
         <v>43</v>
       </c>
@@ -43628,7 +43621,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="58">
+    <row r="829" spans="1:5" ht="57">
       <c r="A829" s="5"/>
       <c r="B829" s="25" t="s">
         <v>895</v>
@@ -43733,7 +43726,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="58">
+    <row r="836" spans="1:5" ht="57">
       <c r="A836" s="5"/>
       <c r="B836" s="25" t="s">
         <v>896</v>
@@ -43838,7 +43831,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="58">
+    <row r="843" spans="1:5" ht="57">
       <c r="A843" s="5"/>
       <c r="B843" s="25" t="s">
         <v>897</v>
@@ -45670,7 +45663,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="972" spans="1:5" ht="29">
+    <row r="972" spans="1:5" ht="28.5">
       <c r="B972">
         <v>21</v>
       </c>
@@ -45684,7 +45677,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="973" spans="1:5" ht="29">
+    <row r="973" spans="1:5">
       <c r="B973">
         <v>22</v>
       </c>
@@ -45712,7 +45705,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="975" spans="1:5" ht="29">
+    <row r="975" spans="1:5" ht="28.5">
       <c r="B975">
         <v>24</v>
       </c>
@@ -45726,7 +45719,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="976" spans="1:5" ht="29">
+    <row r="976" spans="1:5" ht="28.5">
       <c r="B976">
         <v>25</v>
       </c>
@@ -45740,7 +45733,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="977" spans="2:5" ht="29">
+    <row r="977" spans="2:5">
       <c r="B977">
         <v>26</v>
       </c>
@@ -46372,7 +46365,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="1022" spans="1:5" ht="29">
+    <row r="1022" spans="1:5" ht="28.5">
       <c r="B1022">
         <v>21</v>
       </c>
@@ -46386,7 +46379,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="1023" spans="1:5" ht="29">
+    <row r="1023" spans="1:5">
       <c r="B1023">
         <v>22</v>
       </c>
@@ -46414,7 +46407,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="1025" spans="2:5" ht="29">
+    <row r="1025" spans="2:5" ht="28.5">
       <c r="B1025">
         <v>24</v>
       </c>
@@ -46428,7 +46421,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="1026" spans="2:5" ht="29">
+    <row r="1026" spans="2:5" ht="28.5">
       <c r="B1026">
         <v>25</v>
       </c>
@@ -46442,7 +46435,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="1027" spans="2:5" ht="29">
+    <row r="1027" spans="2:5">
       <c r="B1027">
         <v>26</v>
       </c>
@@ -46933,7 +46926,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="1062" spans="1:5" ht="29">
+    <row r="1062" spans="1:5" ht="28.5">
       <c r="A1062" s="5"/>
       <c r="B1062" s="5"/>
       <c r="C1062" s="6" t="s">
@@ -50938,7 +50931,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1329" spans="1:5" ht="43.5">
+    <row r="1329" spans="1:5" ht="42.75">
       <c r="A1329" s="5"/>
       <c r="B1329" t="s">
         <v>17</v>
@@ -51133,7 +51126,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1342" spans="1:5" ht="29">
+    <row r="1342" spans="1:5" ht="28.5">
       <c r="A1342" s="5"/>
       <c r="B1342" s="5" t="s">
         <v>905</v>
@@ -51268,7 +51261,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="1351" spans="1:5" ht="29">
+    <row r="1351" spans="1:5" ht="28.5">
       <c r="A1351" s="5"/>
       <c r="B1351" s="5" t="s">
         <v>859</v>
@@ -51403,7 +51396,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="1360" spans="1:5" ht="29">
+    <row r="1360" spans="1:5" ht="28.5">
       <c r="A1360" s="5"/>
       <c r="B1360" s="5" t="s">
         <v>815</v>
@@ -51538,7 +51531,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="1369" spans="1:5" ht="29">
+    <row r="1369" spans="1:5" ht="28.5">
       <c r="A1369" s="5"/>
       <c r="B1369" s="48" t="s">
         <v>1721</v>
@@ -51673,7 +51666,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="1378" spans="1:5" ht="29">
+    <row r="1378" spans="1:5" ht="28.5">
       <c r="A1378" s="5"/>
       <c r="B1378" s="5" t="s">
         <v>921</v>
@@ -51943,7 +51936,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="1396" spans="1:5" ht="29">
+    <row r="1396" spans="1:5" ht="28.5">
       <c r="A1396" s="5"/>
       <c r="B1396" s="5" t="s">
         <v>18</v>
@@ -52108,7 +52101,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1407" spans="1:5" s="11" customFormat="1" ht="29">
+    <row r="1407" spans="1:5" s="11" customFormat="1" ht="28.5">
       <c r="A1407" s="5"/>
       <c r="B1407" s="5"/>
       <c r="C1407" s="14" t="s">
@@ -52121,7 +52114,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="1408" spans="1:5" ht="29">
+    <row r="1408" spans="1:5" ht="28.5">
       <c r="A1408" s="5"/>
       <c r="B1408" s="5" t="s">
         <v>692</v>
@@ -52226,7 +52219,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1415" spans="1:5" ht="29">
+    <row r="1415" spans="1:5" ht="28.5">
       <c r="A1415" s="5"/>
       <c r="B1415" s="5" t="s">
         <v>693</v>
@@ -52331,7 +52324,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1422" spans="1:5" ht="43.5">
+    <row r="1422" spans="1:5" ht="28.5">
       <c r="A1422" s="5"/>
       <c r="B1422" s="5" t="s">
         <v>694</v>
@@ -52438,7 +52431,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1429" spans="1:5" ht="29">
+    <row r="1429" spans="1:5" ht="28.5">
       <c r="A1429" s="5"/>
       <c r="B1429" s="5" t="s">
         <v>695</v>
@@ -52648,7 +52641,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1443" spans="1:5" ht="29">
+    <row r="1443" spans="1:5" ht="28.5">
       <c r="A1443" s="5"/>
       <c r="B1443" s="5" t="s">
         <v>697</v>
@@ -52753,7 +52746,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1450" spans="1:5" ht="29">
+    <row r="1450" spans="1:5" ht="28.5">
       <c r="A1450" s="5"/>
       <c r="B1450" s="5" t="s">
         <v>134</v>
@@ -52918,7 +52911,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1461" spans="1:5" ht="29">
+    <row r="1461" spans="1:5" ht="28.5">
       <c r="A1461" s="5"/>
       <c r="B1461" s="5"/>
       <c r="C1461" s="21" t="s">
@@ -52931,7 +52924,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="1462" spans="1:5" ht="29">
+    <row r="1462" spans="1:5" ht="28.5">
       <c r="A1462" s="5"/>
       <c r="B1462" s="12" t="s">
         <v>698</v>
@@ -53036,7 +53029,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1469" spans="1:5" ht="29">
+    <row r="1469" spans="1:5" ht="28.5">
       <c r="A1469" s="5"/>
       <c r="B1469" s="12" t="s">
         <v>699</v>
@@ -53141,7 +53134,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1476" spans="1:5" ht="29">
+    <row r="1476" spans="1:5" ht="28.5">
       <c r="A1476" s="5"/>
       <c r="B1476" s="12" t="s">
         <v>700</v>
@@ -53248,7 +53241,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1483" spans="1:5" ht="29">
+    <row r="1483" spans="1:5" ht="28.5">
       <c r="A1483" s="5"/>
       <c r="B1483" s="12" t="s">
         <v>701</v>
@@ -53353,7 +53346,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1490" spans="1:5" ht="29">
+    <row r="1490" spans="1:5" ht="28.5">
       <c r="A1490" s="5"/>
       <c r="B1490" s="12" t="s">
         <v>702</v>
@@ -53458,7 +53451,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1497" spans="1:5" ht="29">
+    <row r="1497" spans="1:5" ht="28.5">
       <c r="A1497" s="5"/>
       <c r="B1497" s="12" t="s">
         <v>703</v>
@@ -53563,7 +53556,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1504" spans="1:5" ht="43.5">
+    <row r="1504" spans="1:5" ht="42.75">
       <c r="B1504" s="48"/>
       <c r="C1504" s="21" t="s">
         <v>1779</v>
@@ -54247,7 +54240,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1553" spans="1:5" ht="29">
+    <row r="1553" spans="1:5" ht="28.5">
       <c r="A1553" s="5"/>
       <c r="B1553" s="5" t="s">
         <v>784</v>
@@ -54412,7 +54405,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1564" spans="1:5" ht="29">
+    <row r="1564" spans="1:5" ht="28.5">
       <c r="A1564" s="5"/>
       <c r="B1564" s="5"/>
       <c r="C1564" s="21" t="s">
@@ -54425,7 +54418,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="1565" spans="1:5" ht="29">
+    <row r="1565" spans="1:5" ht="28.5">
       <c r="A1565" s="12"/>
       <c r="B1565" s="12" t="s">
         <v>787</v>
@@ -54530,7 +54523,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1572" spans="1:5" ht="29">
+    <row r="1572" spans="1:5" ht="28.5">
       <c r="A1572" s="5"/>
       <c r="B1572" s="12" t="s">
         <v>788</v>
@@ -54635,7 +54628,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1579" spans="1:5" ht="29">
+    <row r="1579" spans="1:5" ht="28.5">
       <c r="A1579" s="5"/>
       <c r="B1579" s="12" t="s">
         <v>789</v>
@@ -54742,7 +54735,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1586" spans="1:5" ht="29">
+    <row r="1586" spans="1:5" ht="28.5">
       <c r="A1586" s="5"/>
       <c r="B1586" s="12" t="s">
         <v>790</v>
@@ -54847,7 +54840,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1593" spans="1:5" ht="29">
+    <row r="1593" spans="1:5" ht="28.5">
       <c r="A1593" s="5"/>
       <c r="B1593" s="12" t="s">
         <v>791</v>
@@ -54952,7 +54945,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1600" spans="1:5" ht="29">
+    <row r="1600" spans="1:5" ht="28.5">
       <c r="A1600" s="5"/>
       <c r="B1600" s="12" t="s">
         <v>792</v>
@@ -55057,7 +55050,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1607" spans="1:5" ht="43.5">
+    <row r="1607" spans="1:5" ht="42.75">
       <c r="B1607" s="48"/>
       <c r="C1607" s="21" t="s">
         <v>1841</v>
@@ -55069,7 +55062,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="1608" spans="1:5" ht="29">
+    <row r="1608" spans="1:5" ht="28.5">
       <c r="B1608" s="48" t="s">
         <v>1844</v>
       </c>
@@ -55153,7 +55146,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1614" spans="1:5" ht="29">
+    <row r="1614" spans="1:5" ht="28.5">
       <c r="B1614" s="48" t="s">
         <v>1848</v>
       </c>
@@ -55237,7 +55230,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1620" spans="1:5" ht="29">
+    <row r="1620" spans="1:5" ht="28.5">
       <c r="A1620" s="5"/>
       <c r="B1620" s="5" t="s">
         <v>941</v>
@@ -55402,7 +55395,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1631" spans="1:5" ht="29">
+    <row r="1631" spans="1:5" ht="28.5">
       <c r="A1631" s="5"/>
       <c r="B1631" s="5"/>
       <c r="C1631" s="21" t="s">
@@ -55415,7 +55408,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="1632" spans="1:5" ht="29">
+    <row r="1632" spans="1:5" ht="28.5">
       <c r="A1632" s="12"/>
       <c r="B1632" s="12" t="s">
         <v>943</v>
@@ -55520,7 +55513,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1639" spans="1:5" ht="29">
+    <row r="1639" spans="1:5" ht="28.5">
       <c r="A1639" s="5"/>
       <c r="B1639" s="12" t="s">
         <v>944</v>
@@ -55625,7 +55618,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1646" spans="1:5" ht="29">
+    <row r="1646" spans="1:5" ht="28.5">
       <c r="A1646" s="5"/>
       <c r="B1646" s="12" t="s">
         <v>945</v>
@@ -55732,7 +55725,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1653" spans="1:5" ht="29">
+    <row r="1653" spans="1:5" ht="28.5">
       <c r="A1653" s="5"/>
       <c r="B1653" s="12" t="s">
         <v>946</v>
@@ -55837,7 +55830,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1660" spans="1:5" ht="29">
+    <row r="1660" spans="1:5" ht="28.5">
       <c r="A1660" s="5"/>
       <c r="B1660" s="12" t="s">
         <v>947</v>
@@ -55942,7 +55935,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1667" spans="1:5" ht="29">
+    <row r="1667" spans="1:5" ht="28.5">
       <c r="A1667" s="5"/>
       <c r="B1667" s="12" t="s">
         <v>948</v>
@@ -56047,7 +56040,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1674" spans="1:5" ht="29">
+    <row r="1674" spans="1:5" ht="28.5">
       <c r="B1674" s="48"/>
       <c r="C1674" s="21" t="s">
         <v>1879</v>
@@ -56227,7 +56220,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1687" spans="2:5" ht="29">
+    <row r="1687" spans="2:5" ht="28.5">
       <c r="B1687" s="11" t="s">
         <v>1890</v>
       </c>
@@ -56311,7 +56304,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1693" spans="2:5" ht="29">
+    <row r="1693" spans="2:5" ht="28.5">
       <c r="B1693" s="11" t="s">
         <v>1894</v>
       </c>
@@ -56395,7 +56388,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1699" spans="1:5" ht="29">
+    <row r="1699" spans="1:5" ht="28.5">
       <c r="B1699" s="11" t="s">
         <v>1898</v>
       </c>
@@ -56584,7 +56577,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1712" spans="1:5" ht="43.5">
+    <row r="1712" spans="1:5" ht="42.75">
       <c r="A1712" s="5"/>
       <c r="B1712" s="5"/>
       <c r="C1712" s="6" t="s">
@@ -59749,7 +59742,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1923" spans="1:5" ht="29">
+    <row r="1923" spans="1:5" ht="28.5">
       <c r="A1923" s="5"/>
       <c r="B1923" s="5"/>
       <c r="C1923" s="6" t="s">
@@ -61444,7 +61437,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="2036" spans="1:5" ht="29">
+    <row r="2036" spans="1:5" ht="28.5">
       <c r="A2036" s="5"/>
       <c r="B2036" s="5" t="s">
         <v>23</v>
@@ -61654,7 +61647,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="2050" spans="1:5" ht="29">
+    <row r="2050" spans="1:5" ht="28.5">
       <c r="A2050" s="5"/>
       <c r="B2050" s="5" t="s">
         <v>26</v>
@@ -61849,7 +61842,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="2063" spans="1:5" ht="72.5">
+    <row r="2063" spans="1:5" ht="71.25">
       <c r="A2063" s="5"/>
       <c r="B2063" s="5" t="s">
         <v>12</v>
@@ -62629,7 +62622,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="2115" spans="1:5" ht="29">
+    <row r="2115" spans="1:5" ht="28.5">
       <c r="A2115" s="5"/>
       <c r="B2115" s="5">
         <v>31</v>
@@ -62644,7 +62637,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="2116" spans="1:5" ht="43.5">
+    <row r="2116" spans="1:5" ht="28.5">
       <c r="A2116" s="5"/>
       <c r="B2116" s="5">
         <v>32</v>
@@ -62689,7 +62682,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="2119" spans="1:5" ht="29">
+    <row r="2119" spans="1:5" ht="28.5">
       <c r="A2119" s="5"/>
       <c r="B2119" s="5">
         <v>51</v>
@@ -62704,7 +62697,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="2120" spans="1:5" ht="29">
+    <row r="2120" spans="1:5" ht="28.5">
       <c r="A2120" s="5"/>
       <c r="B2120" s="5">
         <v>52</v>
@@ -63574,7 +63567,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="2178" spans="1:5" ht="29">
+    <row r="2178" spans="1:5" ht="28.5">
       <c r="A2178" s="5"/>
       <c r="B2178" s="5">
         <v>31</v>
@@ -63589,7 +63582,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="2179" spans="1:5" ht="43.5">
+    <row r="2179" spans="1:5" ht="28.5">
       <c r="A2179" s="5"/>
       <c r="B2179" s="5">
         <v>32</v>
@@ -63634,7 +63627,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="2182" spans="1:5" ht="29">
+    <row r="2182" spans="1:5" ht="28.5">
       <c r="A2182" s="5"/>
       <c r="B2182" s="5">
         <v>51</v>
@@ -63649,7 +63642,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="2183" spans="1:5" ht="29">
+    <row r="2183" spans="1:5" ht="28.5">
       <c r="A2183" s="5"/>
       <c r="B2183" s="5">
         <v>52</v>
@@ -63724,7 +63717,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="2188" spans="1:5" ht="29">
+    <row r="2188" spans="1:5" ht="28.5">
       <c r="A2188" s="5"/>
       <c r="B2188" s="5" t="s">
         <v>142</v>
@@ -63904,7 +63897,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="2200" spans="1:5" ht="58">
+    <row r="2200" spans="1:5" ht="57">
       <c r="A2200" s="5"/>
       <c r="B2200" s="5" t="s">
         <v>53</v>
@@ -64159,7 +64152,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="2217" spans="1:5" ht="29">
+    <row r="2217" spans="1:5" ht="28.5">
       <c r="A2217" s="5"/>
       <c r="B2217" s="5" t="s">
         <v>143</v>
@@ -64394,7 +64387,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C97DEC3-E03C-4C2D-A881-D575004AB0FC}">
   <dimension ref="B1:C51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1">
@@ -64404,7 +64397,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="2" spans="2:3" ht="58">
+    <row r="2" spans="2:3" ht="57">
       <c r="B2">
         <v>11</v>
       </c>
@@ -64412,7 +64405,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="3" spans="2:3" ht="87">
+    <row r="3" spans="2:3" ht="85.5">
       <c r="B3">
         <v>12</v>
       </c>
@@ -64420,7 +64413,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="116">
+    <row r="4" spans="2:3" ht="114">
       <c r="B4">
         <v>13</v>
       </c>
@@ -64428,7 +64421,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="29">
+    <row r="5" spans="2:3">
       <c r="B5">
         <v>14</v>
       </c>
@@ -64436,7 +64429,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="29">
+    <row r="6" spans="2:3" ht="28.5">
       <c r="B6">
         <v>15</v>
       </c>
@@ -64444,7 +64437,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="29">
+    <row r="7" spans="2:3" ht="28.5">
       <c r="B7">
         <v>16</v>
       </c>
@@ -64452,7 +64445,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="29">
+    <row r="8" spans="2:3" ht="28.5">
       <c r="B8">
         <v>19</v>
       </c>
@@ -64460,7 +64453,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="58">
+    <row r="10" spans="2:3" ht="57">
       <c r="B10">
         <v>20</v>
       </c>
@@ -64468,7 +64461,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="174">
+    <row r="11" spans="2:3" ht="156.75">
       <c r="B11">
         <v>21</v>
       </c>
@@ -64476,7 +64469,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="145">
+    <row r="12" spans="2:3" ht="142.5">
       <c r="B12">
         <v>22</v>
       </c>
@@ -64484,7 +64477,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="58">
+    <row r="13" spans="2:3" ht="57">
       <c r="B13">
         <v>23</v>
       </c>
@@ -64492,7 +64485,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="203">
+    <row r="14" spans="2:3" ht="199.5">
       <c r="B14">
         <v>24</v>
       </c>
@@ -64500,7 +64493,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="174">
+    <row r="15" spans="2:3" ht="156.75">
       <c r="B15">
         <v>25</v>
       </c>
@@ -64508,7 +64501,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="145">
+    <row r="16" spans="2:3" ht="142.5">
       <c r="B16">
         <v>26</v>
       </c>
@@ -64516,7 +64509,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="87">
+    <row r="17" spans="2:3" ht="85.5">
       <c r="B17">
         <v>27</v>
       </c>
@@ -64524,7 +64517,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="72.5">
+    <row r="18" spans="2:3" ht="71.25">
       <c r="B18">
         <v>29</v>
       </c>
@@ -64532,7 +64525,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="43.5">
+    <row r="20" spans="2:3" ht="42.75">
       <c r="B20">
         <v>30</v>
       </c>
@@ -64540,7 +64533,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="58">
+    <row r="21" spans="2:3" ht="57">
       <c r="B21">
         <v>31</v>
       </c>
@@ -64548,7 +64541,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="130.5">
+    <row r="22" spans="2:3" ht="128.25">
       <c r="B22">
         <v>32</v>
       </c>
@@ -64556,7 +64549,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="130.5">
+    <row r="23" spans="2:3" ht="128.25">
       <c r="B23">
         <v>32</v>
       </c>
@@ -64564,7 +64557,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="87">
+    <row r="24" spans="2:3" ht="71.25">
       <c r="B24">
         <v>33</v>
       </c>
@@ -64572,7 +64565,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="72.5">
+    <row r="25" spans="2:3" ht="71.25">
       <c r="B25">
         <v>34</v>
       </c>
@@ -64580,7 +64573,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="72.5">
+    <row r="26" spans="2:3" ht="71.25">
       <c r="B26">
         <v>35</v>
       </c>
@@ -64588,7 +64581,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="116">
+    <row r="27" spans="2:3" ht="114">
       <c r="B27">
         <v>36</v>
       </c>
@@ -64596,7 +64589,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="58">
+    <row r="28" spans="2:3" ht="57">
       <c r="B28">
         <v>39</v>
       </c>
@@ -64604,7 +64597,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="30" spans="2:3" ht="43.5">
+    <row r="30" spans="2:3" ht="28.5">
       <c r="B30">
         <v>40</v>
       </c>
@@ -64612,7 +64605,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="58">
+    <row r="31" spans="2:3" ht="42.75">
       <c r="B31">
         <v>41</v>
       </c>
@@ -64620,7 +64613,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="32" spans="2:3" ht="159.5">
+    <row r="32" spans="2:3" ht="156.75">
       <c r="B32">
         <v>42</v>
       </c>
@@ -64628,7 +64621,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="87">
+    <row r="33" spans="2:3" ht="85.5">
       <c r="B33">
         <v>43</v>
       </c>
@@ -64636,7 +64629,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="34" spans="2:3" ht="87">
+    <row r="34" spans="2:3" ht="85.5">
       <c r="B34">
         <v>44</v>
       </c>
@@ -64644,7 +64637,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="35" spans="2:3" ht="101.5">
+    <row r="35" spans="2:3" ht="99.75">
       <c r="B35">
         <v>45</v>
       </c>
@@ -64652,7 +64645,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="36" spans="2:3" ht="116">
+    <row r="36" spans="2:3" ht="114">
       <c r="B36">
         <v>46</v>
       </c>
@@ -64660,7 +64653,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="37" spans="2:3" ht="72.5">
+    <row r="37" spans="2:3" ht="71.25">
       <c r="B37">
         <v>47</v>
       </c>
@@ -64668,7 +64661,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="38" spans="2:3" ht="43.5">
+    <row r="38" spans="2:3" ht="42.75">
       <c r="B38">
         <v>48</v>
       </c>
@@ -64676,7 +64669,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="39" spans="2:3" ht="58">
+    <row r="39" spans="2:3" ht="42.75">
       <c r="B39">
         <v>49</v>
       </c>
@@ -64692,7 +64685,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="43" spans="2:3" ht="43.5">
+    <row r="43" spans="2:3" ht="42.75">
       <c r="B43">
         <v>91</v>
       </c>
@@ -64700,7 +64693,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="44" spans="2:3" ht="43.5">
+    <row r="44" spans="2:3" ht="42.75">
       <c r="B44">
         <v>92</v>
       </c>
@@ -64708,7 +64701,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="45" spans="2:3" ht="43.5">
+    <row r="45" spans="2:3" ht="42.75">
       <c r="B45">
         <v>93</v>
       </c>
@@ -64716,7 +64709,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="46" spans="2:3" ht="87">
+    <row r="46" spans="2:3" ht="85.5">
       <c r="B46">
         <v>94</v>
       </c>
@@ -64724,7 +64717,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="47" spans="2:3" ht="101.5">
+    <row r="47" spans="2:3" ht="99.75">
       <c r="B47">
         <v>95</v>
       </c>
@@ -64732,7 +64725,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="48" spans="2:3" ht="87">
+    <row r="48" spans="2:3" ht="85.5">
       <c r="B48">
         <v>96</v>
       </c>
@@ -64740,7 +64733,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="49" spans="2:3" ht="58">
+    <row r="49" spans="2:3" ht="57">
       <c r="B49">
         <v>97</v>
       </c>
@@ -64748,7 +64741,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="50" spans="2:3" ht="29">
+    <row r="50" spans="2:3" ht="28.5">
       <c r="B50">
         <v>98</v>
       </c>
@@ -64756,7 +64749,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="51" spans="2:3" ht="29">
+    <row r="51" spans="2:3" ht="28.5">
       <c r="B51">
         <v>99</v>
       </c>
@@ -64772,79 +64765,79 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8CC5BC-7E89-4F56-8A15-CB519E182F49}">
   <dimension ref="A1:R23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:18" ht="14.25" customHeight="1">
       <c r="A1" s="70" t="s">
         <v>1916</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="94" t="s">
         <v>1917</v>
       </c>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="94"/>
+      <c r="R1" s="94"/>
     </row>
     <row r="2" spans="1:18" ht="14.25" customHeight="1">
       <c r="A2" s="70" t="s">
         <v>1918</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="95" t="s">
         <v>1919</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-      <c r="Q2" s="93"/>
-      <c r="R2" s="93"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="95"/>
+      <c r="R2" s="95"/>
     </row>
     <row r="3" spans="1:18" ht="14.25" customHeight="1">
       <c r="A3" s="70" t="s">
         <v>1920</v>
       </c>
-      <c r="B3" s="93" t="s">
+      <c r="B3" s="95" t="s">
         <v>1921</v>
       </c>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="93"/>
-      <c r="R3" s="93"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="95"/>
+      <c r="N3" s="95"/>
+      <c r="O3" s="95"/>
+      <c r="P3" s="95"/>
+      <c r="Q3" s="95"/>
+      <c r="R3" s="95"/>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="72"/>
@@ -65226,7 +65219,7 @@
         <v>0.74580000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="69" customFormat="1" ht="29">
+    <row r="11" spans="1:18" s="69" customFormat="1" ht="28.5">
       <c r="A11" s="77" t="s">
         <v>1949</v>
       </c>
